--- a/artfynd/A 4771-2026 artfynd.xlsx
+++ b/artfynd/A 4771-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97211243</v>
+        <v>121302352</v>
       </c>
       <c r="B2" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223246</v>
+        <v>103008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,19 +708,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>STENUNGSUND, Boh</t>
+          <t>Stenungsund, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>315522.7478366939</v>
+        <v>315672</v>
       </c>
       <c r="R2" t="n">
-        <v>6438916.234015551</v>
+        <v>6438974</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,34 +747,14 @@
           <t>Norum</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>17BFD938-9A20-4E44-ADAD-777B6CFAE522</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-05-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-05-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>{C0670AEC-801A-4F1B-83FB-D636D840525D}</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,31 +769,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Stenström</t>
+          <t>Per Österman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sanna Persson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Per Österman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121303263</v>
+        <v>121302354</v>
       </c>
       <c r="B3" t="n">
-        <v>57726</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,16 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -854,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>315528</v>
+        <v>315585</v>
       </c>
       <c r="R3" t="n">
-        <v>6438853</v>
+        <v>6438962</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -913,6 +884,227 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121303263</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stenungsund, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>315528</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6438853</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Österman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Österman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>97211243</v>
+      </c>
+      <c r="B5" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>STENUNGSUND, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>315523</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6438916</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norum</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>17BFD938-9A20-4E44-ADAD-777B6CFAE522</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2016-05-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2016-05-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>{C0670AEC-801A-4F1B-83FB-D636D840525D}</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sanna Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4771-2026 artfynd.xlsx
+++ b/artfynd/A 4771-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121302352</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121302354</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121303263</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,8 +1125,19 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97211243</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>